--- a/product_order_forms/013_gaming_system_order_form--product_order_forms.xlsx
+++ b/product_order_forms/013_gaming_system_order_form--product_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1114,8 +1114,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'card'}</t>
+          <t>card</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Card'}</t>
+          <t>Card</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'ps4'}</t>
+          <t>ps4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'PS4'}</t>
+          <t>PS4</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'xbox'}</t>
+          <t>xbox</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Xbox'}</t>
+          <t>Xbox</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'switch'}</t>
+          <t>switch</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Switch'}</t>
+          <t>Switch</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1483,12 +1483,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1517,12 +1517,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1534,12 +1534,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1568,12 +1568,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
